--- a/Tickets/Demo/Raffle_26Jun26.xlsx
+++ b/Tickets/Demo/Raffle_26Jun26.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbndawula/Documents/GitHub/advanced-raffle-draws/Tickets/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C77C833-F933-3442-A578-2E7CE009BEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559BF63F-FEEF-AB4C-BDC3-C0B15E87F66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11300" yWindow="-12700" windowWidth="21600" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -353,13 +353,37 @@
   </si>
   <si>
     <t>141, 262</t>
+  </si>
+  <si>
+    <t>140, 245, 281, 294, 155</t>
+  </si>
+  <si>
+    <t>Aiden (Angel)</t>
+  </si>
+  <si>
+    <t>Calvin CJ</t>
+  </si>
+  <si>
+    <t>39, 149, 277</t>
+  </si>
+  <si>
+    <t>Maureen</t>
+  </si>
+  <si>
+    <t>85, 288</t>
+  </si>
+  <si>
+    <t>Angeline</t>
+  </si>
+  <si>
+    <t>51, 129, 280</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,6 +395,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -396,14 +427,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -679,12 +728,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="40.5" customWidth="1"/>
     <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -737,7 +787,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D51" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
+        <f t="shared" ref="D3:D55" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
         <v>3</v>
       </c>
       <c r="E3" t="s">
@@ -847,7 +897,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
@@ -1057,7 +1107,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C23" t="s">
@@ -1357,7 +1407,7 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C43" t="s">
@@ -1488,8 +1538,69 @@
         <v>2</v>
       </c>
     </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F47" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F55" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Tickets/Demo/Raffle_26Jun26.xlsx
+++ b/Tickets/Demo/Raffle_26Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbndawula/Documents/GitHub/advanced-raffle-draws/Tickets/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559BF63F-FEEF-AB4C-BDC3-C0B15E87F66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7A77EC-44B3-A044-B489-B02C76C19E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="116">
   <si>
     <t>#</t>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>51, 129, 280</t>
+  </si>
+  <si>
+    <t>Bridget Atuhaire</t>
+  </si>
+  <si>
+    <t>42, 81, 151, 189, 263</t>
   </si>
 </sst>
 </file>
@@ -435,24 +441,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -728,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -787,7 +776,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D55" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
+        <f t="shared" ref="D3:D56" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
         <v>3</v>
       </c>
       <c r="E3" t="s">
@@ -1596,6 +1585,21 @@
       <c r="D55">
         <f t="shared" si="0"/>
         <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Tickets/Demo/Raffle_26Jun26.xlsx
+++ b/Tickets/Demo/Raffle_26Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbndawula/Documents/GitHub/advanced-raffle-draws/Tickets/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7A77EC-44B3-A044-B489-B02C76C19E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0B74FB-D53E-9D44-BA15-77894BC98E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="119">
   <si>
     <t>#</t>
   </si>
@@ -383,6 +383,15 @@
   </si>
   <si>
     <t>42, 81, 151, 189, 263</t>
+  </si>
+  <si>
+    <t>Mike Mugisha</t>
+  </si>
+  <si>
+    <t>228, 264, 289, 272, 297</t>
+  </si>
+  <si>
+    <t>Total Bought</t>
   </si>
 </sst>
 </file>
@@ -413,20 +422,41 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -435,8 +465,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,37 +747,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="40.5" customWidth="1"/>
     <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F1">
-        <f>SUM(D2:D47)</f>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -764,8 +794,12 @@
       <c r="E2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <f>SUM(D:D)</f>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -776,14 +810,14 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D56" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
+        <f t="shared" ref="D3:D57" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
         <v>3</v>
       </c>
       <c r="E3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -801,7 +835,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -816,7 +850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -834,7 +868,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -852,7 +886,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -867,7 +901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -882,11 +916,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
@@ -897,7 +931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -915,7 +949,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -933,7 +967,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -951,7 +985,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -969,7 +1003,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -984,7 +1018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1096,7 +1130,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C23" t="s">
@@ -1396,7 +1430,7 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C43" t="s">
@@ -1531,7 +1565,7 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C52" t="s">
@@ -1576,7 +1610,7 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C55" t="s">
@@ -1598,6 +1632,21 @@
         <v>115</v>
       </c>
       <c r="D56">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>

--- a/Tickets/Demo/Raffle_26Jun26.xlsx
+++ b/Tickets/Demo/Raffle_26Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbndawula/Documents/GitHub/advanced-raffle-draws/Tickets/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0B74FB-D53E-9D44-BA15-77894BC98E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94A9E4D-0CCF-0842-B8FB-E4C8677BE486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="121">
   <si>
     <t>#</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t>Total Bought</t>
+  </si>
+  <si>
+    <t>Sheila Ampa</t>
+  </si>
+  <si>
+    <t>97, 107, 226</t>
   </si>
 </sst>
 </file>
@@ -747,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -796,7 +802,7 @@
       </c>
       <c r="G2">
         <f>SUM(D:D)</f>
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -810,7 +816,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D57" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
+        <f t="shared" ref="D3:D58" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
         <v>3</v>
       </c>
       <c r="E3" t="s">
@@ -1649,6 +1655,21 @@
       <c r="D57">
         <f t="shared" si="0"/>
         <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Tickets/Demo/Raffle_26Jun26.xlsx
+++ b/Tickets/Demo/Raffle_26Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbndawula/Documents/GitHub/advanced-raffle-draws/Tickets/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94A9E4D-0CCF-0842-B8FB-E4C8677BE486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E98C93-7559-FC44-AFBE-4673B5754AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="145">
   <si>
     <t>#</t>
   </si>
@@ -398,6 +398,78 @@
   </si>
   <si>
     <t>97, 107, 226</t>
+  </si>
+  <si>
+    <t>Eusuph</t>
+  </si>
+  <si>
+    <t>Alexandrina</t>
+  </si>
+  <si>
+    <t>Hoza</t>
+  </si>
+  <si>
+    <t>268, 284, 286</t>
+  </si>
+  <si>
+    <t>53, 134, 143</t>
+  </si>
+  <si>
+    <t>52, 56, 78</t>
+  </si>
+  <si>
+    <t>Herbert Nazeba</t>
+  </si>
+  <si>
+    <t>Christine Benet</t>
+  </si>
+  <si>
+    <t>Ivan Hannington</t>
+  </si>
+  <si>
+    <t>43, 125, 126, 128, 131, 132, 161, 162, 164, 293</t>
+  </si>
+  <si>
+    <t>147, 179</t>
+  </si>
+  <si>
+    <t>Susie Samantha</t>
+  </si>
+  <si>
+    <t>108, 117, 167, 172, 176</t>
+  </si>
+  <si>
+    <t>Daniel Tasingika</t>
+  </si>
+  <si>
+    <t>156, 246</t>
+  </si>
+  <si>
+    <t>Claire Agaba</t>
+  </si>
+  <si>
+    <t>136, 138, 142, 229, 251</t>
+  </si>
+  <si>
+    <t>Davis Baguma</t>
+  </si>
+  <si>
+    <t>Najib Mwanje</t>
+  </si>
+  <si>
+    <t>Mr &amp; Mrs Waibi</t>
+  </si>
+  <si>
+    <t>158, 182, 184</t>
+  </si>
+  <si>
+    <t>252, 257, 261, 265, 267, 271, 278, 279, 296, 249</t>
+  </si>
+  <si>
+    <t>241, 243, 153</t>
+  </si>
+  <si>
+    <t>165, 183, 193, 196, 241</t>
   </si>
 </sst>
 </file>
@@ -753,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -802,7 +874,7 @@
       </c>
       <c r="G2">
         <f>SUM(D:D)</f>
-        <v>246</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -816,7 +888,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D58" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
+        <f t="shared" ref="D3:D66" si="0">IF(ISBLANK(C3),"",LEN(TRIM(C3))-LEN(SUBSTITUTE(TRIM(C3),",",""))+1)</f>
         <v>3</v>
       </c>
       <c r="E3" t="s">
@@ -1672,8 +1744,188 @@
         <v>3</v>
       </c>
     </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>127</v>
+      </c>
+      <c r="C62" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" t="s">
+        <v>133</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" t="s">
+        <v>137</v>
+      </c>
+      <c r="D67">
+        <f t="shared" ref="D67:D70" si="1">IF(ISBLANK(C67),"",LEN(TRIM(C67))-LEN(SUBSTITUTE(TRIM(C67),",",""))+1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" t="s">
+        <v>143</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" t="s">
+        <v>144</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F55" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/Tickets/Demo/Raffle_26Jun26.xlsx
+++ b/Tickets/Demo/Raffle_26Jun26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbndawula/Documents/GitHub/advanced-raffle-draws/Tickets/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E98C93-7559-FC44-AFBE-4673B5754AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2C725F-6490-5843-B40D-86EA2D182BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -466,10 +466,10 @@
     <t>252, 257, 261, 265, 267, 271, 278, 279, 296, 249</t>
   </si>
   <si>
-    <t>241, 243, 153</t>
-  </si>
-  <si>
     <t>165, 183, 193, 196, 241</t>
+  </si>
+  <si>
+    <t>135, 243, 153</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1902,7 @@
         <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D69">
         <f t="shared" si="1"/>
@@ -1917,7 +1917,7 @@
         <v>138</v>
       </c>
       <c r="C70" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D70">
         <f t="shared" si="1"/>
